--- a/slide_classification/TCGA_Results/Averaging/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7340909090909091</v>
+        <v>0.7363636363636363</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8443223443223443</v>
+        <v>0.8406593406593407</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8092391304347826</v>
+        <v>0.8097826086956521</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6179775280898876</v>
+        <v>0.6170411985018727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7514074779844809</v>
+        <v>0.7509616960551254</v>
       </c>
     </row>
     <row r="7">
@@ -578,26 +579,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[81  7]
- [ 6  9]]</t>
+          <t>[[81, 7], [6, 9]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[82  2]
- [ 8  5]]</t>
+          <t>[[82, 2], [8, 5]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[84  8]
- [10 10]]</t>
+          <t>[[84, 8], [10, 10]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[85  4]
- [ 8  4]]</t>
+          <t>[[85, 4], [8, 4]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7766990291262136</v>
+        <v>0.7281553398058253</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7835051546391752</v>
+        <v>0.7731958762886598</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8125</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8035720855453076</v>
+        <v>0.7484813683800569</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7587121212121212</v>
+        <v>0.7303030303030302</v>
       </c>
       <c r="C9" t="n">
-        <v>0.679945054945055</v>
+        <v>0.7065018315018315</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7684782608695653</v>
+        <v>0.7304347826086957</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6938202247191011</v>
+        <v>0.673689138576779</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7252389154364606</v>
+        <v>0.7102321957475841</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.673015873015873</v>
+        <v>0.6302564102564102</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6339622641509435</v>
+        <v>0.6400134952766532</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7257142857142858</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6683087027914614</v>
+        <v>0.594753086419753</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6752502814181409</v>
+        <v>0.6329224146548709</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8035136384650947</v>
+        <v>0.7650983320886233</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8052129935810154</v>
+        <v>0.8002838181894069</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8248979591836735</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8510787039295062</v>
+        <v>0.7813470235912481</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8211758237898223</v>
+        <v>0.7801346744197004</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8075757575757576</v>
+        <v>0.8121212121212121</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7362637362637363</v>
+        <v>0.7976190476190477</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8326086956521739</v>
+        <v>0.766304347826087</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7162921348314607</v>
+        <v>0.7172284644194757</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7731850810807821</v>
+        <v>0.7733182679964556</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[69 19]
- [ 4 11]]</t>
+          <t>[[64, 24], [4, 11]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[69 15]
- [ 6  7]]</t>
+          <t>[[67, 17], [5, 8]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[77 15]
- [ 6 14]]</t>
+          <t>[[70, 22], [6, 14]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[79 10]
- [ 6  6]]</t>
+          <t>[[68, 21], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[74, 15], [6, 10]]</t>
+          <t>[[67, 21], [5, 10]]</t>
         </is>
       </c>
     </row>
@@ -762,7 +755,7 @@
         <v>0.8640776699029126</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8556701030927835</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="D14" t="n">
         <v>0.8303571428571429</v>
@@ -771,7 +764,7 @@
         <v>0.8613861386138614</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8528727636166751</v>
+        <v>0.8580274027919328</v>
       </c>
     </row>
     <row r="15">
@@ -784,7 +777,7 @@
         <v>0.6715909090909091</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5265567765567766</v>
+        <v>0.5709706959706959</v>
       </c>
       <c r="D15" t="n">
         <v>0.5836956521739131</v>
@@ -793,7 +786,7 @@
         <v>0.524812734082397</v>
       </c>
       <c r="F15" t="n">
-        <v>0.576664017975999</v>
+        <v>0.5877674978294788</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +799,7 @@
         <v>0.6918803418803419</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5231741573033708</v>
+        <v>0.5912921348314606</v>
       </c>
       <c r="D16" t="n">
         <v>0.5999247978943411</v>
@@ -815,7 +808,7 @@
         <v>0.5248655913978495</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5849612221189758</v>
+        <v>0.6019907165009982</v>
       </c>
     </row>
     <row r="17">
@@ -828,7 +821,7 @@
         <v>0.8551323541614805</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8146212208965598</v>
+        <v>0.8411039036256226</v>
       </c>
       <c r="D17" t="n">
         <v>0.7951145489216556</v>
@@ -837,7 +830,7 @@
         <v>0.8297136165229426</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8236454351256597</v>
+        <v>0.8302661058079253</v>
       </c>
     </row>
     <row r="18">
@@ -850,7 +843,7 @@
         <v>0.6920454545454546</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6726190476190477</v>
+        <v>0.7184065934065934</v>
       </c>
       <c r="D18" t="n">
         <v>0.6959239130434782</v>
@@ -859,7 +852,7 @@
         <v>0.5903558052434458</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6627360551128566</v>
+        <v>0.674182941559743</v>
       </c>
     </row>
     <row r="19">
@@ -870,26 +863,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[83  5]
- [ 9  6]]</t>
+          <t>[[83, 5], [9, 6]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[82  2]
- [12  1]]</t>
+          <t>[[83, 1], [11, 2]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[89  3]
- [16  4]]</t>
+          <t>[[89, 3], [16, 4]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[86  3]
- [11  1]]</t>
+          <t>[[86, 3], [11, 1]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1016,26 +1005,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[68 20]
- [ 5 10]]</t>
+          <t>[[68, 20], [5, 10]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[55 29]
- [ 7  6]]</t>
+          <t>[[55, 29], [7, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[64 28]
- [ 6 14]]</t>
+          <t>[[64, 28], [6, 14]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[60 29]
- [ 7  5]]</t>
+          <t>[[60, 29], [7, 5]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7106060606060607</v>
+        <v>0.7659090909090909</v>
       </c>
       <c r="C27" t="n">
         <v>0.6538461538461539</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6673913043478261</v>
+        <v>0.6478260869565218</v>
       </c>
       <c r="E27" t="n">
         <v>0.524812734082397</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6391640632206094</v>
+        <v>0.6480985164485409</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7358974358974359</v>
+        <v>0.7659090909090909</v>
       </c>
       <c r="C28" t="n">
         <v>0.7098703888334995</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6879256965944273</v>
+        <v>0.671875</v>
       </c>
       <c r="E28" t="n">
         <v>0.5248655913978495</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6646397781808031</v>
+        <v>0.6681300177851099</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8758277321384118</v>
+        <v>0.883495145631068</v>
       </c>
       <c r="C29" t="n">
         <v>0.8850150579190263</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8276426360017691</v>
+        <v>0.8225446428571429</v>
       </c>
       <c r="E29" t="n">
         <v>0.8297136165229426</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8545497606455374</v>
+        <v>0.8551921157325451</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8628787878787879</v>
+        <v>0.8553030303030303</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8434065934065934</v>
+        <v>0.815018315018315</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7190217391304347</v>
+        <v>0.7119565217391305</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6451310861423222</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7676095516395346</v>
+        <v>0.7634065454168043</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[84  4]
- [ 8  7]]</t>
+          <t>[[82, 6], [6, 9]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[84  0]
- [ 9  4]]</t>
+          <t>[[84, 0], [9, 4]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[86  6]
- [12  8]]</t>
+          <t>[[87, 5], [13, 7]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[86  3]
- [11  1]]</t>
+          <t>[[86, 3], [11, 1]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[85, 3], [10, 5]]</t>
+          <t>[[85, 4], [10, 5]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ConchV1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8727918643398578</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.02106951890051877</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6978366747037363</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0422770856638864</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7140619640785029</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.03079895586916037</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8663038158489241</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01810911787717969</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7509616960551254</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0861007697745433</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[83, 5], [8, 7]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ConchV1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>413</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7484813683800569</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01628768354147198</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7102321957475841</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02323947912727157</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6329224146548709</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02575346173620638</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7801346744197004</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01297648744946808</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7733182679964556</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03637120256629979</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[67, 21], [5, 10]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ConchV1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>413</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8580274027919328</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01693372102184957</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5877674978294788</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05312339181961118</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6019907165009982</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.05947091167630647</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8302661058079253</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.02220205713811587</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.674182941559743</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.04943293279000301</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[85, 3], [12, 3]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ConchV1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>413</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6815351151609291</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05043598498874378</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6302713062056003</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.07899866846385502</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5651185040584532</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.06818944892487266</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7264310173448685</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0379693447481334</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6822712643975468</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1180221647372851</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[62, 26], [6, 9]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ConchV1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>413</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8728458733440011</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02526042566316184</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6480985164485409</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08531093883822803</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6681300177851099</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.08922125093847129</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8551921157325451</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02917824870181005</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7634065454168043</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.07454958331901623</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[85, 4], [10, 5]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Averaging/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7281553398058253</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="C8" t="n">
         <v>0.7731958762886598</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>0.7767857142857143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7425742574257426</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7484813683800569</v>
+        <v>0.7921142575878404</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7303030303030302</v>
+        <v>0.7530303030303029</v>
       </c>
       <c r="C9" t="n">
         <v>0.7065018315018315</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7304347826086957</v>
+        <v>0.7467391304347826</v>
       </c>
       <c r="E9" t="n">
-        <v>0.673689138576779</v>
+        <v>0.6633895131086143</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7102321957475841</v>
+        <v>0.7174151945188828</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6302564102564102</v>
+        <v>0.6641304347826087</v>
       </c>
       <c r="C10" t="n">
         <v>0.6400134952766532</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.691051528191548</v>
       </c>
       <c r="E10" t="n">
-        <v>0.594753086419753</v>
+        <v>0.6576271186440679</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6329224146548709</v>
+        <v>0.6632056442237195</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7650983320886233</v>
+        <v>0.7958632334318277</v>
       </c>
       <c r="C11" t="n">
         <v>0.8002838181894069</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7738095238095238</v>
+        <v>0.7956762976623949</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7813470235912481</v>
+        <v>0.8540359120657829</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7801346744197004</v>
+        <v>0.8114648153373532</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8121212121212121</v>
+        <v>0.7704545454545453</v>
       </c>
       <c r="C12" t="n">
         <v>0.7976190476190477</v>
       </c>
       <c r="D12" t="n">
-        <v>0.766304347826087</v>
+        <v>0.7994565217391304</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7172284644194757</v>
+        <v>0.701310861423221</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7733182679964556</v>
+        <v>0.7672102440589861</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[64, 24], [4, 11]]</t>
+          <t>[[68, 20], [4, 11]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[70, 22], [6, 14]]</t>
+          <t>[[73, 19], [6, 14]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[68, 21], [5, 7]]</t>
+          <t>[[81, 8], [7, 5]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[67, 21], [5, 10]]</t>
+          <t>[[72, 16], [6, 10]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7484813683800569</v>
+        <v>0.7921142575878404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01628768354147198</v>
+        <v>0.03445644266370412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7102321957475841</v>
+        <v>0.7174151945188828</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02323947912727157</v>
+        <v>0.03593815839767601</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6329224146548709</v>
+        <v>0.6632056442237195</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02575346173620638</v>
+        <v>0.01833878548291378</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7801346744197004</v>
+        <v>0.8114648153373532</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01297648744946808</v>
+        <v>0.02464751317177349</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7733182679964556</v>
+        <v>0.7672102440589861</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03637120256629979</v>
+        <v>0.03974220641050141</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[67, 21], [5, 10]]</t>
+          <t>[[72, 16], [6, 10]]</t>
         </is>
       </c>
     </row>
